--- a/code/df_roi_v.xlsx
+++ b/code/df_roi_v.xlsx
@@ -478,30 +478,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>898K</t>
+          <t>870K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05397244405831969</v>
+        <v>0.05515904657078451</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -511,124 +511,124 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>559K</t>
+          <t>564K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>40.9%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>59.6%</t>
-        </is>
-      </c>
       <c r="D3" t="n">
-        <v>0.03863281662015593</v>
+        <v>0.03732256485560451</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>-10.3%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>-8.2%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-14.0%</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-0.3569940692701778</v>
+        <v>-1.6905166745115</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.49640305366167</v>
+        <v>-0.0886937528101206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>155K</t>
+          <t>158K</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>8.7%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>8.8%</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
       <c r="D4" t="n">
-        <v>0.06530955150575159</v>
+        <v>0.06627790398111603</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>-6.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-11.1%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-12.2%</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.444969796582111</v>
+        <v>11.13174255134077</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.80038454852556</v>
+        <v>5.501464979705428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>251K</t>
+          <t>255K</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>11.3%</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>25.5%</t>
-        </is>
-      </c>
       <c r="D5" t="n">
-        <v>0.01254923805355509</v>
+        <v>0.01198399516242397</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>-14.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>-13.1%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-11.5%</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>15.03209214110372</v>
+        <v>16.26145723716388</v>
       </c>
       <c r="I5" t="n">
-        <v>10.07498538118488</v>
+        <v>14.8150346664782</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +639,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>46.4%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>23.6%</t>
-        </is>
-      </c>
       <c r="D6" t="n">
-        <v>0.03687315634218289</v>
+        <v>0.03230769230769231</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>-17.2%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>-51.2%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-34.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -667,42 +667,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>164K</t>
+          <t>169K</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>70.3%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>142.0%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>368.8%</t>
-        </is>
-      </c>
       <c r="D7" t="n">
-        <v>0.01054295616221803</v>
+        <v>0.01070034307346504</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>-55.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>-54.6%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-69.1%</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.707240280781886</v>
+        <v>-37.67707944679174</v>
       </c>
       <c r="I7" t="n">
-        <v>-41.25564013121777</v>
+        <v>2.013285829429567</v>
       </c>
     </row>
     <row r="8">
@@ -719,83 +719,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>154K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>36.4%</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>43.2%</t>
-        </is>
-      </c>
       <c r="D9" t="n">
-        <v>0.03423867286164208</v>
+        <v>0.0356120744357105</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>-33.8%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>-35.5%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-33.4%</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.176012049013786</v>
+        <v>39.74216019365493</v>
       </c>
       <c r="I9" t="n">
-        <v>30.99990549351686</v>
+        <v>-4.984253615160017</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>115.1%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>135.6%</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>131.8%</t>
-        </is>
-      </c>
       <c r="D10" t="n">
-        <v>0.1413777577667717</v>
+        <v>0.1435954468140782</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>-22.4%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>-22.9%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-21.5%</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>92.73310206906248</v>
+        <v>116.7665670767512</v>
       </c>
       <c r="I10" t="n">
-        <v>106.9860143291117</v>
+        <v>97.91496246926505</v>
       </c>
     </row>
     <row r="11">
@@ -806,37 +806,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04208794763300094</v>
+        <v>0.04212178977806873</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.22</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>122.2649216104907</v>
+        <v>152.199649047318</v>
       </c>
       <c r="I11" t="n">
-        <v>65.73537561286389</v>
+        <v>127.0574222018178</v>
       </c>
     </row>
   </sheetData>

--- a/code/df_roi_v.xlsx
+++ b/code/df_roi_v.xlsx
@@ -478,30 +478,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>870K</t>
+          <t>898K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.05515904657078451</v>
+        <v>0.05475762916220883</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -511,124 +511,124 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>564K</t>
+          <t>550K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.03732256485560451</v>
+        <v>0.03821936154476582</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>-6.2%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>-10.3%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-8.2%</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-1.6905166745115</v>
+        <v>-2.318024838964561</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0886937528101206</v>
+        <v>0.6177153121963652</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>158K</t>
+          <t>157K</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.06627790398111603</v>
+        <v>0.06735625887733199</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11.13174255134077</v>
+        <v>10.99239269891961</v>
       </c>
       <c r="I4" t="n">
-        <v>5.501464979705428</v>
+        <v>7.071593514585994</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>255K</t>
+          <t>269K</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01198399516242397</v>
+        <v>0.01193202944894772</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>16.26145723716388</v>
+        <v>2.704148214326474</v>
       </c>
       <c r="I5" t="n">
-        <v>14.8150346664782</v>
+        <v>6.402392733651041</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +639,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.03230769230769231</v>
+        <v>0.05743243243243244</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -667,42 +667,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>169K</t>
+          <t>165K</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>142.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01070034307346504</v>
+        <v>0.01193350724989383</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-37.67707944679174</v>
+        <v>-20.01692874215384</v>
       </c>
       <c r="I7" t="n">
-        <v>2.013285829429567</v>
+        <v>-16.40811114913409</v>
       </c>
     </row>
     <row r="8">
@@ -719,83 +719,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>154K</t>
+          <t>140K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0356120744357105</v>
+        <v>0.03997431598473228</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>39.74216019365493</v>
+        <v>-24.24883652998722</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.984253615160017</v>
+        <v>41.35818491590209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>16K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>117.8%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1435954468140782</v>
+        <v>0.1457940399849114</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>116.7665670767512</v>
+        <v>100.6647480630555</v>
       </c>
       <c r="I10" t="n">
-        <v>97.91496246926505</v>
+        <v>108.7191463834078</v>
       </c>
     </row>
     <row r="11">
@@ -806,37 +806,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04212178977806873</v>
+        <v>0.0427712319247783</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19.22</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>152.199649047318</v>
+        <v>34.65013984518818</v>
       </c>
       <c r="I11" t="n">
-        <v>127.0574222018178</v>
+        <v>196.2575408635291</v>
       </c>
     </row>
   </sheetData>
